--- a/resources/user_import.xlsx
+++ b/resources/user_import.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\Desktop\Дем\Dem\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\Desktop\На дем 1 вариант\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72C8EDE-4DD3-4C36-BBE7-3CE4E1418911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22837FE3-E7BA-4970-9D22-5A9190F3F609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Роль сотрудника</t>
   </si>
@@ -43,9 +42,6 @@
     <t>Пароль</t>
   </si>
   <si>
-    <t>Администратор</t>
-  </si>
-  <si>
     <t>2L6KZG</t>
   </si>
   <si>
@@ -76,30 +72,6 @@
     <t>JlFRCZ</t>
   </si>
   <si>
-    <t>Сазонов Руслан Германович</t>
-  </si>
-  <si>
-    <t>Одинцов Серафим Артёмович</t>
-  </si>
-  <si>
-    <t>Степанов Михаил Артёмович</t>
-  </si>
-  <si>
-    <t>Михайлюк Анна Вячеславовна</t>
-  </si>
-  <si>
-    <t>Ситдикова Елена Анатольевна</t>
-  </si>
-  <si>
-    <t>Ворсин Петр Евгеньевич</t>
-  </si>
-  <si>
-    <t>Старикова Елена Павловна</t>
-  </si>
-  <si>
-    <t>Никифорова Весения Николаевна</t>
-  </si>
-  <si>
     <t>94d5ous@gmail.com</t>
   </si>
   <si>
@@ -128,15 +100,6 @@
   </si>
   <si>
     <t>wpmrc3do@tutanota.com</t>
-  </si>
-  <si>
-    <t>Менеджер</t>
-  </si>
-  <si>
-    <t>Авторизированный клиент</t>
-  </si>
-  <si>
-    <t>id_user</t>
   </si>
 </sst>
 </file>
@@ -528,230 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24.75" customWidth="1"/>
-    <col min="3" max="3" width="38.5" customWidth="1"/>
-    <col min="4" max="4" width="36.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="1"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A878748-C26C-4723-8675-1E47FE4DD0CD}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.75" customWidth="1"/>
@@ -774,130 +514,166 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{1E1F6DE4-4B79-40F2-8028-6A01E9AC6E9A}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{48962851-4D5B-446A-8908-54A102C3D2CB}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{6C55AEFB-2C89-4AE4-91B5-09057849458D}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{62F6B3CA-56AF-4411-9557-E09BA4BF5221}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{1A940A2A-3935-46FB-A96A-DC19ADB6BA47}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{295F0528-B712-4BB5-9BC6-0A81028DA109}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{59371D9C-2737-40CA-AC5F-2AA9CDCDE606}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{6C98C871-AF44-4884-BAA2-82D51ECA0FAB}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{1C790E73-178B-4D41-8800-1123009E4F17}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{7EA6A685-AADB-4FF5-AA9E-17ECEB98C8EB}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
